--- a/public/templates/diet_plans_bulk_upload_template.xlsx
+++ b/public/templates/diet_plans_bulk_upload_template.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +13,14 @@
     <sheet name="References" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,43 +29,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5D50"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -77,54 +56,35 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -207,44 +167,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -271,32 +231,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -323,24 +265,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -352,142 +276,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -498,16 +446,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.33203125" customWidth="1" min="1" max="1"/>
-    <col width="39.6640625" customWidth="1" min="2" max="2"/>
-    <col width="17.5546875" customWidth="1" min="3" max="3"/>
-    <col width="13.44140625" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="13.44140625" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,248 +503,237 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>guidance_description</t>
+          <t>is_personalized_plan</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>guidance_tips</t>
+          <t>guidance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Sinus Relief &amp; Respiratory Comfort Diet Plan</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Kapha</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Sinus | Cough &amp; Cold | Lung Wellness</t>
         </is>
       </c>
-      <c r="F2" s="7" t="b">
+      <c r="F2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>This diet plan supports sinus relief and respiratory comfort with warm, light, Kapha-pacifying meals.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Keep meals warm and freshly prepared | Avoid cold drinks and ice cream | Prefer light dinner | Stay hydrated with warm water</t>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Prefer warm, freshly cooked meals throughout the day, especially during the monsoon season. || Favor soft, easy-to-digest foods such as moong dal, khichdi, cooked vegetables, soups, and porridges.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Anxiety &amp; Stress Calming Mind Diet Plan</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Vata</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>all_seasons</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Anxiety | Stress</t>
         </is>
       </c>
-      <c r="F3" s="7" t="b">
+      <c r="F3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>This diet plan is designed to stabilize the mind and nourish the nervous system for Vata constitution.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Maintain regular meal timings | Include warm beverages like herbal teas | Avoid cold, raw, and processed foods | Incorporate gentle yoga or walking</t>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Prefer warm, freshly cooked meals throughout the day, especially during the monsoon season. || Favor soft, easy-to-digest foods such as moong dal, khichdi, cooked vegetables, soups, and porridges.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Joint &amp; Muscle Comfort Support Diet Plan</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Vata-Kapha</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Joint Pain | Muscle Pain | Back Pain</t>
         </is>
       </c>
-      <c r="F4" s="7" t="b">
+      <c r="F4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>This diet plan is designed to stabilize the mind and nourish the nervous system for Vata constitution.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Maintain regular meal timings | Include warm beverages like herbal teas | Avoid cold, raw, and processed foods | Incorporate gentle yoga or walking</t>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Prefer warm, freshly cooked meals throughout the day, especially during the monsoon season. || Favor soft, easy-to-digest foods such as moong dal, khichdi, cooked vegetables, soups, and porridges.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Liver Detox &amp; Fatty Liver Care Diet Plan</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Pitta</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Liver Detox | Fatty Liver | Digestive Liver</t>
         </is>
       </c>
-      <c r="F5" s="7" t="b">
+      <c r="F5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>This diet plan is designed to stabilize the mind and nourish the nervous system for Vata constitution.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Maintain regular meal timings | Include warm beverages like herbal teas | Avoid cold, raw, and processed foods | Incorporate gentle yoga or walking</t>
+      <c r="H5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Prefer warm, freshly cooked meals throughout the day, especially during the monsoon season. || Favor soft, easy-to-digest foods such as moong dal, khichdi, cooked vegetables, soups, and porridges.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>PCOS / PCOD Hormonal Balance Diet Plan</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Kapha</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>PCOS | PCOD | Menstrual Disorders</t>
         </is>
       </c>
-      <c r="F6" s="7" t="b">
+      <c r="F6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>This diet plan is designed to stabilize the mind and nourish the nervous system for Vata constitution.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Maintain regular meal timings | Include warm beverages like herbal teas | Avoid cold, raw, and processed foods | Incorporate gentle yoga or walking</t>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Prefer warm, freshly cooked meals throughout the day, especially during the monsoon season. || Favor soft, easy-to-digest foods such as moong dal, khichdi, cooked vegetables, soups, and porridges.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -805,17 +744,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.77734375" customWidth="1" min="1" max="1"/>
-    <col width="11.77734375" customWidth="1" min="3" max="3"/>
-    <col width="35.5546875" customWidth="1" min="4" max="4"/>
-    <col width="11.77734375" customWidth="1" min="5" max="5"/>
-    <col width="31.109375" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="15.5546875" customWidth="1" min="8" max="8"/>
-    <col width="16.77734375" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -880,3552 +822,3272 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26.4" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Warm turmeric-ginger water</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Clears sinuses and reduces congestion</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Boil water with turmeric, ginger and black pepper | Drink warm</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="7" t="n">
+      <c r="K2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="26.4" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Steam inhalation herbs (tulsi + mint)</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>As needed</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Helps open nasal passages</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Add tulsi and mint to hot water for steam</t>
         </is>
       </c>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
-      <c r="L3" s="7" t="n"/>
-    </row>
-    <row r="4" ht="39.6" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Moong dal khichdi with ghee and black pepper</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Light and easy to digest during congestion</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Cook moong + rice with turmeric | Finish with ghee and black pepper</t>
         </is>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="26.4" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tulsi-ginger herbal tea</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1 cup</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Supports respiratory comfort</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Boil tulsi leaves and ginger | Strain</t>
         </is>
       </c>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="26.4" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Warm vegetable clear soup (carrot, bottle gourd)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Hydrating and soothing</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Boil vegetables with cumin and rock salt</t>
         </is>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="L6" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="26.4" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Red rice with lauki-carrot sabzi</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Warm, grounding meal</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Cook red rice | Prepare simple vegetable sabzi with cumin</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="K7" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="2" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Moong dal tadka</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Light protein</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Temper moong dal with cumin and ghee</t>
         </is>
       </c>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="26.4" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Clear vegetable soup with black pepper</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Light evening meal to reduce Kapha</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Boil mixed vegetables | Season with black pepper and cumin</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K9" s="7" t="n">
+      <c r="K9" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="L9" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Warm lemon water with cinnamon</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Helps thin mucus</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Squeeze lemon in warm water | Add pinch of cinnamon</t>
         </is>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="K10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="26.4" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Ragi porridge with ginger</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Warm and nourishing</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Cook ragi with water/milk and ginger | Add little jaggery if needed</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="K11" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Roasted makhana with black pepper</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1 small bowl</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Light snack</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dry roast makhana | Sprinkle black pepper and rock salt</t>
         </is>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="K12" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Foxtail millet with mixed vegetable curry</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Gluten-free and light</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Cook millet | Prepare vegetable curry with mild spices</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="K13" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="2" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="26.4" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Moong soup with spinach and garlic</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Easy to digest at night</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Pressure cook moong with spinach and garlic | Blend lightly</t>
         </is>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="2" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="15" ht="26.4" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Warm ajwain-jeera water</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Supports digestion and reduces Kapha</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Boil ajwain and cumin seeds | Drink warm</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="K15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="26.4" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Vegetable upma (dalia) with curry leaves</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Warm and saturating</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Roast dalia | Cook with vegetables and mustard seeds</t>
         </is>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="2" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Hand-pounded rice with bottle gourd dal</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Simple and soothing</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Cook rice | Prepare bottle gourd with toor/moong dal</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="2" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Clear carrot-beet soup</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Light and warming</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Boil carrot and beetroot with cumin | Blend partially</t>
         </is>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="J18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="K18" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="19" ht="26.4" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Warm saffron-almond milk</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1 cup</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Calms Vata and soothes the mind</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Warm milk | Add saffron strands and crushed almonds</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K19" s="7" t="n">
+      <c r="K19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="2" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="20" ht="26.4" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Soaked walnuts + flaxseeds</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>4 walnuts + 1 tsp flax</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Omega-3 for brain and mood support</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Soak overnight</t>
         </is>
       </c>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="26.4" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Ragi porridge with cardamom and ghee</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Grounding and stabilising</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Cook ragi in milk/water with cardamom | Finish with ghee</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="K21" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="2" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="26.4" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Roasted pumpkin seeds + 2 dates</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1 handful + 2 dates</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Magnesium for calm nerves</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Dry roast pumpkin seeds</t>
         </is>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="K22" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="23" ht="26.4" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Moong khichdi with ghee and cumin</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Easy to digest and Vata-pacifying</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Cook moong + rice with turmeric and cumin | Add ghee</t>
         </is>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="K23" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" s="2" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Steamed bottle gourd with black pepper</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>½ bowl</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Light and calming</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Steam and season</t>
         </is>
       </c>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Vegetable clear soup with ghee</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Light evening meal</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Boil mixed vegetables | Finish with ghee and cumin</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="J25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K25" s="7" t="n">
+      <c r="K25" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="L25" s="2" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="26" ht="26.4" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Warm milk with nutmeg and cardamom</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1 cup</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Promotes mental calm</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Warm milk | Add pinch of nutmeg and cardamom</t>
         </is>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I26" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K26" s="7" t="n">
+      <c r="K26" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="L26" s="2" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="27" ht="26.4" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Broken wheat (dalia) porridge with ghee</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Warm and heavy for Vata</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Cook dalia in milk/water | Add ghee and little jaggery</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="I27" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="J27" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="L27" s="2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="28" ht="26.4" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Banana + roasted sesame seeds</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1 banana + 1 tsp sesame</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Potassium and calcium for calm</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Dry roast sesame</t>
         </is>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="J28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K28" s="7" t="n">
+      <c r="K28" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="L28" s="2" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="29" ht="26.4" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Red rice with sesame-tempered vegetables</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Nourishing and grounding</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Cook red rice | Temper vegetables with sesame seeds</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="J29" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K29" s="7" t="n">
+      <c r="K29" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="L29" s="2" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Moong dal with ghee</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Light protein</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Cook and finish with ghee</t>
         </is>
       </c>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
-    </row>
-    <row r="31" ht="26.4" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Soft khichdi with extra ghee</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Classic calming dinner</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Cook rice + moong until soft | Add extra ghee</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="I31" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="J31" s="7" t="n">
+      <c r="J31" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K31" s="7" t="n">
+      <c r="K31" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="L31" s="2" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="32" ht="26.4" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="B32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Warm water with turmeric and black pepper</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Anti-inflammatory start</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Mix turmeric and black pepper in warm water</t>
         </is>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I32" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J32" s="7" t="n">
+      <c r="J32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="K32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="L32" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="26.4" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="B33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Soaked almonds + flaxseeds</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>5 almonds + 1 tsp flax</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Healthy fats for joint lubrication</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Soak overnight</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="7" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
-    </row>
-    <row r="34" ht="26.4" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Ragi porridge with sesame and jaggery</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Calcium and warming</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Cook ragi with sesame powder and little jaggery</t>
         </is>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="I34" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="J34" s="7" t="n">
+      <c r="J34" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K34" s="7" t="n">
+      <c r="K34" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="L34" s="7" t="n">
+      <c r="L34" s="2" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="35" ht="26.4" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Roasted makhana with ghee and black pepper</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1 small bowl</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Light and warming snack</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Roast in ghee | Add black pepper</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I35" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="J35" s="7" t="n">
+      <c r="J35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="7" t="n">
+      <c r="K35" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="L35" s="7" t="n">
+      <c r="L35" s="2" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="36" ht="26.4" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="B36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Foxtail millet with methi-vegetable sabzi</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Supports joint comfort</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Cook millet | Prepare methi + mixed vegetable sabzi</t>
         </is>
       </c>
-      <c r="I36" s="7" t="n">
+      <c r="I36" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="J36" s="7" t="n">
+      <c r="J36" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K36" s="7" t="n">
+      <c r="K36" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L36" s="7" t="n">
+      <c r="L36" s="2" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="37" ht="26.4" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="B37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Moong dal with garlic and ghee</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Protein and anti-inflammatory</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Temper with garlic and ghee</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-    </row>
-    <row r="38" ht="26.4" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Clear soup with drumstick, carrot and spinach</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Light and mineral-rich</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Boil vegetables with cumin and turmeric</t>
         </is>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="I38" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="J38" s="7" t="n">
+      <c r="J38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K38" s="7" t="n">
+      <c r="K38" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="L38" s="7" t="n">
+      <c r="L38" s="2" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="39" ht="26.4" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Warm ginger-turmeric milk</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1 cup</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Reduces inflammation</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Warm milk with ginger and turmeric</t>
         </is>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="I39" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="J39" s="7" t="n">
+      <c r="J39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K39" s="7" t="n">
+      <c r="K39" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L39" s="7" t="n">
+      <c r="L39" s="2" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="40" ht="26.4" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Vegetable dalia upma with sesame</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Warm and saturating</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Cook dalia with vegetables and sesame seeds</t>
         </is>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="I40" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="J40" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="K40" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="L40" s="7" t="n">
+      <c r="L40" s="2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="41" ht="26.4" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
+      <c r="B41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Handful of roasted peanuts + dates</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1 handful + 2 dates</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Energy and healthy fats</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Lightly roast peanuts</t>
         </is>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="I41" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="J41" s="7" t="n">
+      <c r="J41" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K41" s="7" t="n">
+      <c r="K41" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L41" s="7" t="n">
+      <c r="L41" s="2" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="42" ht="26.4" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n">
+      <c r="B42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Red rice with sesame-tempered ridge gourd and carrot</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Nourishing for muscles and joints</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Cook rice | Temper vegetables with sesame</t>
         </is>
       </c>
-      <c r="I42" s="7" t="n">
+      <c r="I42" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="J42" s="7" t="n">
+      <c r="J42" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K42" s="7" t="n">
+      <c r="K42" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="L42" s="7" t="n">
+      <c r="L42" s="2" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="43" ht="26.4" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B43" s="7" t="n">
+      <c r="B43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Soft moong khichdi with ghee and ajwain</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Easy to digest at night</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Cook until soft | Add ghee and ajwain</t>
         </is>
       </c>
-      <c r="I43" s="7" t="n">
+      <c r="I43" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="J43" s="7" t="n">
+      <c r="J43" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K43" s="7" t="n">
+      <c r="K43" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="L43" s="7" t="n">
+      <c r="L43" s="2" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="44" ht="26.4" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="B44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Warm lemon water with cumin</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Supports liver cleansing</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Squeeze lemon in warm water | Add cumin powder</t>
         </is>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="I44" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J44" s="7" t="n">
+      <c r="J44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="7" t="n">
+      <c r="K44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L44" s="7" t="n">
+      <c r="L44" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="26.4" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B45" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="B45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Soaked fenugreek seeds</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1 tsp</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Supports metabolism and liver</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Soak overnight</t>
         </is>
       </c>
-      <c r="I45" s="7" t="n"/>
-      <c r="J45" s="7" t="n"/>
-      <c r="K45" s="7" t="n"/>
-      <c r="L45" s="7" t="n"/>
-    </row>
-    <row r="46" ht="26.4" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Moong sprouts salad with cucumber and lemon</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Light and detoxifying</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Mix sprouts with cucumber, tomato, lemon and rock salt</t>
         </is>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="I46" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="J46" s="7" t="n">
+      <c r="J46" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K46" s="7" t="n">
+      <c r="K46" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="L46" s="7" t="n">
+      <c r="L46" s="2" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="47" ht="26.4" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B47" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="B47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Coconut water</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Hydrating and cooling for Pitta</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Fresh tender coconut water</t>
         </is>
       </c>
-      <c r="I47" s="7" t="n">
+      <c r="I47" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="J47" s="7" t="n">
+      <c r="J47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K47" s="7" t="n">
+      <c r="K47" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L47" s="7" t="n">
+      <c r="L47" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Foxtail millet with bottle gourd and spinach</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Light on liver</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Cook millet with vegetables and mild spices</t>
         </is>
       </c>
-      <c r="I48" s="7" t="n">
+      <c r="I48" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="J48" s="7" t="n">
+      <c r="J48" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K48" s="7" t="n">
+      <c r="K48" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="L48" s="7" t="n">
+      <c r="L48" s="2" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="B49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thin cucumber-mint raita</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>½ bowl</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Cooling</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Use diluted curd</t>
         </is>
       </c>
-      <c r="I49" s="7" t="n"/>
-      <c r="J49" s="7" t="n"/>
-      <c r="K49" s="7" t="n"/>
-      <c r="L49" s="7" t="n"/>
-    </row>
-    <row r="50" ht="26.4" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="B50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Clear vegetable soup (lauki, carrot, beans)</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Very light evening meal</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Boil vegetables with cumin and coriander</t>
         </is>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="I50" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="J50" s="7" t="n">
+      <c r="J50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K50" s="7" t="n">
+      <c r="K50" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="L50" s="7" t="n">
+      <c r="L50" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="51" ht="26.4" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n">
+      <c r="B51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Warm jeera-ajwain water</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Stimulates digestion and liver</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Boil cumin and ajwain | Drink warm</t>
         </is>
       </c>
-      <c r="I51" s="7" t="n">
+      <c r="I51" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J51" s="7" t="n">
+      <c r="J51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="7" t="n">
+      <c r="K51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L51" s="7" t="n">
+      <c r="L51" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="26.4" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
+      <c r="B52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Ragi porridge (plain) with flaxseeds</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>High fibre and gentle</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Cook ragi | Top with ground flaxseeds</t>
         </is>
       </c>
-      <c r="I52" s="7" t="n">
+      <c r="I52" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="J52" s="7" t="n">
+      <c r="J52" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K52" s="7" t="n">
+      <c r="K52" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="L52" s="7" t="n">
+      <c r="L52" s="2" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
+      <c r="B53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Roasted makhana with rock salt</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1 small bowl</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Light snack</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Dry roast makhana</t>
         </is>
       </c>
-      <c r="I53" s="7" t="n">
+      <c r="I53" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="J53" s="7" t="n">
+      <c r="J53" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K53" s="7" t="n">
+      <c r="K53" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="L53" s="7" t="n">
+      <c r="L53" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="54" ht="26.4" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B54" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Quinoa with mixed vegetable stir-fry</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Complete protein and fibre</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Cook quinoa | Stir-fry vegetables with minimal oil</t>
         </is>
       </c>
-      <c r="I54" s="7" t="n">
+      <c r="I54" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="J54" s="7" t="n">
+      <c r="J54" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="K54" s="7" t="n">
+      <c r="K54" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L54" s="7" t="n">
+      <c r="L54" s="2" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="55" ht="26.4" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B55" s="7" t="n">
+      <c r="B55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Moong dal soup with garlic and spinach</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Easy on liver and digestion</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Pressure cook and blend lightly</t>
         </is>
       </c>
-      <c r="I55" s="7" t="n">
+      <c r="I55" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="J55" s="7" t="n">
+      <c r="J55" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K55" s="7" t="n">
+      <c r="K55" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L55" s="7" t="n">
+      <c r="L55" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Warm lemon-ginger water</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Liver supportive</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Add lemon and ginger to warm water</t>
         </is>
       </c>
-      <c r="I56" s="7" t="n">
+      <c r="I56" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J56" s="7" t="n">
+      <c r="J56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K56" s="7" t="n">
+      <c r="K56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L56" s="7" t="n">
+      <c r="L56" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Vegetable upma with minimal oil</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Light and saturating</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Cook dalia/quinoa with plenty of vegetables</t>
         </is>
       </c>
-      <c r="I57" s="7" t="n">
+      <c r="I57" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="J57" s="7" t="n">
+      <c r="J57" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K57" s="7" t="n">
+      <c r="K57" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="L57" s="7" t="n">
+      <c r="L57" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Red rice with lauki-chana dal</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Balanced and light</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Cook rice | Prepare chana dal with bottle gourd</t>
         </is>
       </c>
-      <c r="I58" s="7" t="n">
+      <c r="I58" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="J58" s="7" t="n">
+      <c r="J58" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K58" s="7" t="n">
+      <c r="K58" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="L58" s="7" t="n">
+      <c r="L58" s="2" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B59" s="7" t="n">
+      <c r="B59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Zucchini and spinach clear soup</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Very light for night</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Boil and blend lightly with cumin</t>
         </is>
       </c>
-      <c r="I59" s="7" t="n">
+      <c r="I59" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="J59" s="7" t="n">
+      <c r="J59" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K59" s="7" t="n">
+      <c r="K59" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L59" s="7" t="n">
+      <c r="L59" s="2" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="60" ht="26.4" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="B60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Warm lemon water with cinnamon</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Supports insulin sensitivity</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Add lemon and cinnamon to warm water</t>
         </is>
       </c>
-      <c r="I60" s="7" t="n">
+      <c r="I60" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J60" s="7" t="n">
+      <c r="J60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K60" s="7" t="n">
+      <c r="K60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L60" s="7" t="n">
+      <c r="L60" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="61" ht="26.4" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="B61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Soaked methi seeds + flaxseeds</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1 tsp each</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Hormonal and blood sugar support</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Soak overnight</t>
         </is>
       </c>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
-      <c r="K61" s="7" t="n"/>
-      <c r="L61" s="7" t="n"/>
-    </row>
-    <row r="62" ht="26.4" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="B62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Moong sprouts salad with cucumber and coriander</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>High protein and low GI</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Mix sprouts with vegetables, lemon and rock salt</t>
         </is>
       </c>
-      <c r="I62" s="7" t="n">
+      <c r="I62" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="J62" s="7" t="n">
+      <c r="J62" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K62" s="7" t="n">
+      <c r="K62" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="L62" s="7" t="n">
+      <c r="L62" s="2" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="63" ht="26.4" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B63" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="B63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Herbal tea (ginger + tulsi)</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1 cup</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Supports metabolism</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Boil and steep</t>
         </is>
       </c>
-      <c r="I63" s="7" t="n"/>
-      <c r="J63" s="7" t="n"/>
-      <c r="K63" s="7" t="n"/>
-      <c r="L63" s="7" t="n"/>
-    </row>
-    <row r="64" ht="26.4" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="B64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Handful of soaked almonds + walnuts</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>6 almonds + 2 walnuts</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Healthy fats for hormones</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Soak overnight</t>
         </is>
       </c>
-      <c r="I64" s="7" t="n">
+      <c r="I64" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="J64" s="7" t="n">
+      <c r="J64" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K64" s="7" t="n">
+      <c r="K64" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="L64" s="7" t="n">
+      <c r="L64" s="2" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="65" ht="26.4" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B65" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="B65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Foxtail millet khichdi with spinach and bottle gourd</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Light and fibre-rich</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Cook millet with vegetables and mild spices</t>
         </is>
       </c>
-      <c r="I65" s="7" t="n">
+      <c r="I65" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="J65" s="7" t="n">
+      <c r="J65" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K65" s="7" t="n">
+      <c r="K65" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L65" s="7" t="n">
+      <c r="L65" s="2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="66" ht="26.4" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="B66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Clear vegetable soup with black pepper</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Light Kapha-friendly dinner</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Boil mixed vegetables | Season well</t>
         </is>
       </c>
-      <c r="I66" s="7" t="n">
+      <c r="I66" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="J66" s="7" t="n">
+      <c r="J66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K66" s="7" t="n">
+      <c r="K66" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="L66" s="7" t="n">
+      <c r="L66" s="2" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="67" ht="26.4" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B67" s="7" t="n">
+      <c r="B67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Warm water with apple cider vinegar or lemon + cinnamon</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1 glass</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Supports metabolism</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Mix in warm water</t>
         </is>
       </c>
-      <c r="I67" s="7" t="n">
+      <c r="I67" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J67" s="7" t="n">
+      <c r="J67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K67" s="7" t="n">
+      <c r="K67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L67" s="7" t="n">
+      <c r="L67" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="68" ht="26.4" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n">
+      <c r="B68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Ragi porridge with flaxseeds and berries</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1 bowl</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Low GI and hormone supportive</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Cook ragi | Top with flax and berries</t>
         </is>
       </c>
-      <c r="I68" s="7" t="n">
+      <c r="I68" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="J68" s="7" t="n">
+      <c r="J68" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K68" s="7" t="n">
+      <c r="K68" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="L68" s="7" t="n">
+      <c r="L68" s="2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="69" ht="26.4" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B69" s="7" t="n">
+      <c r="B69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Roasted makhana with black pepper</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1 small bowl</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Light and Kapha-pacifying</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Dry roast and season</t>
         </is>
       </c>
-      <c r="I69" s="7" t="n">
+      <c r="I69" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="J69" s="7" t="n">
+      <c r="J69" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K69" s="7" t="n">
+      <c r="K69" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L69" s="7" t="n">
+      <c r="L69" s="2" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="70" ht="26.4" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B70" s="7" t="n">
+      <c r="B70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Quinoa + mixed vegetable stir-fry with tofu</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1 plate</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Complete protein and high fibre</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Cook quinoa | Stir-fry vegetables and tofu</t>
         </is>
       </c>
-      <c r="I70" s="7" t="n">
+      <c r="I70" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="J70" s="7" t="n">
+      <c r="J70" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="K70" s="7" t="n">
+      <c r="K70" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="L70" s="7" t="n">
+      <c r="L70" s="2" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="71" ht="26.4" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B71" s="7" t="n">
+      <c r="B71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Moong dal soup with spinach</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1 large bowl</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Easy to digest at night</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>youtube.abc.com | youtube.xyz.com</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Pressure cook and season</t>
         </is>
       </c>
-      <c r="I71" s="7" t="n">
+      <c r="I71" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="J71" s="7" t="n">
+      <c r="J71" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K71" s="7" t="n">
+      <c r="K71" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="L71" s="7" t="n">
+      <c r="L71" s="2" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4435,15 +4097,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.88671875" customWidth="1" min="1" max="1"/>
-    <col width="13.88671875" customWidth="1" min="2" max="2"/>
-    <col width="18.77734375" customWidth="1" min="3" max="3"/>
-    <col width="22.44140625" customWidth="1" min="4" max="4"/>
-    <col width="69" customWidth="1" min="5" max="5"/>
-    <col width="42.33203125" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4469,524 +4133,575 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>food_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>image_url</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>caption</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>is_cover</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="43.2" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>DIET_PLAN</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>https://ayurmuni.s3.ap-south-1.amazonaws.com/diet_plan_files/379856e9c23f438fbf3998818642e1a9.png</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Sinus Relief &amp; Respiratory Comfort Cover</t>
         </is>
       </c>
-      <c r="G2" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="43.2" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>DIET_PLAN</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>https://ayurmuni.s3.ap-south-1.amazonaws.com/diet_plan_files/326f1a15f177491c8a7f7c3d7e7a34f1.png</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Warm respiratory-friendly meals</t>
         </is>
       </c>
-      <c r="G3" s="8" t="b">
+      <c r="H3" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="28.8" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Warm turmeric-ginger water</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>https://ayurmuni.s3.ap-south-1.amazonaws.com/diet_plan_files/25ea7070399d43218b55109bd8aa1546.png</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Turmeric-ginger water</t>
         </is>
       </c>
-      <c r="G4" s="8" t="b">
+      <c r="H4" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="28.8" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>DP001</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Moong dal khichdi with ghee and black pepper</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>https://ayurmuni.s3.ap-south-1.amazonaws.com/diet_plan_files/0736d4322ec04d4a84e77fa8dcaa0085.png</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Moong khichdi with tulsi tea</t>
         </is>
       </c>
-      <c r="G5" s="8" t="b">
+      <c r="H5" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="43.2" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>DIET_PLAN</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>https://ayurmuni.s3.ap-south-1.amazonaws.com/diet_plan_files/5e6c19eec834437d87ae151f6f3bebf4.png</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Anxiety &amp; Stress Calming Cover</t>
         </is>
       </c>
-      <c r="G6" s="8" t="b">
+      <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Warm saffron-almond milk</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>https://cdn.ayurmuni.com/diet-plans/anxiety/day1-morning.webp</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Saffron almond milk</t>
         </is>
       </c>
-      <c r="G7" s="8" t="b">
+      <c r="H7" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>DP002</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Vegetable clear soup with ghee</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>https://cdn.ayurmuni.com/diet-plans/anxiety/day1-dinner.webp</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Calming vegetable soup</t>
         </is>
       </c>
-      <c r="G8" s="8" t="b">
+      <c r="H8" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="43.2" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>DIET_PLAN</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>https://ayurmuni.s3.ap-south-1.amazonaws.com/diet_plan_files/1ce70bf79bcd4162b98b6131b14bedf0.png</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Joint &amp; Muscle Comfort Cover</t>
         </is>
       </c>
-      <c r="G9" s="8" t="b">
+      <c r="H9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Warm water with turmeric and black pepper</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>https://cdn.ayurmuni.com/diet-plans/joint/day1-morning.webp</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Turmeric black pepper water</t>
         </is>
       </c>
-      <c r="G10" s="8" t="b">
+      <c r="H10" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>DP003</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Foxtail millet with methi-vegetable sabzi</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>https://cdn.ayurmuni.com/diet-plans/joint/day1-lunch.webp</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Millet with methi sabzi</t>
         </is>
       </c>
-      <c r="G11" s="8" t="b">
+      <c r="H11" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="43.2" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>DIET_PLAN</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>https://ayurmuni.s3.ap-south-1.amazonaws.com/diet_plan_files/751ff70352644281b1253c8be4124640.png</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Liver Detox &amp; Fatty Liver Cover</t>
         </is>
       </c>
-      <c r="G12" s="8" t="b">
+      <c r="H12" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Warm lemon water with cumin</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>https://cdn.ayurmuni.com/diet-plans/liver/day1-morning.webp</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Lemon cumin water</t>
         </is>
       </c>
-      <c r="G13" s="8" t="b">
+      <c r="H13" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>DP004</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Moong sprouts salad with cucumber and lemon</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>https://cdn.ayurmuni.com/diet-plans/liver/day1-breakfast.webp</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Moong sprouts salad</t>
         </is>
       </c>
-      <c r="G14" s="8" t="b">
+      <c r="H14" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="43.2" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>DIET_PLAN</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>https://ayurmuni.s3.ap-south-1.amazonaws.com/diet_plan_files/3da4c2a52e8f47d79a55eba45fe71be6.png</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>PCOS / PCOD Hormonal Balance Cover</t>
         </is>
       </c>
-      <c r="G15" s="8" t="b">
+      <c r="H15" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Warm lemon water with cinnamon</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>https://cdn.ayurmuni.com/diet-plans/pcod/day1-morning.webp</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Lemon cinnamon water + methi</t>
         </is>
       </c>
-      <c r="G16" s="8" t="b">
+      <c r="H16" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>DP005</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Foxtail millet khichdi with spinach and bottle gourd</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>https://cdn.ayurmuni.com/diet-plans/pcod/day1-lunch.webp</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Millet khichdi with vegetables</t>
         </is>
       </c>
-      <c r="G17" s="8" t="b">
+      <c r="H17" s="2" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId8"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4997,13 +4712,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="20.44140625" customWidth="1" min="2" max="2"/>
-    <col width="21.5546875" customWidth="1" min="3" max="3"/>
-    <col width="21.21875" customWidth="1" min="4" max="4"/>
-    <col width="16.6640625" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5012,44 +4727,44 @@
           <t>disease_name</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>prakriti</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>meal_time</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>image_scope</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Sinus</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Vata</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>morning</t>
         </is>
@@ -5061,22 +4776,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Asthma</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Pitta</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>breakfast</t>
         </is>
@@ -5088,271 +4803,363 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Cough &amp; Cold</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Kapha</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>midday</t>
         </is>
       </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Anxiety</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Vata-Pitta</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>lunch</t>
         </is>
       </c>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Stress</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>monsoon</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Pitta-Vata</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>dinner</t>
         </is>
       </c>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Bladder Health</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>all_seasons</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Vata-Kapha</t>
         </is>
       </c>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Urinary Tract Care</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Kapha-Vata</t>
         </is>
       </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Joint Pain</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Pitta-Kapha</t>
         </is>
       </c>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Muscle Pain</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Kapha-Pitta</t>
         </is>
       </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Back Pain</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Tridosha</t>
         </is>
       </c>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Liver Detox</t>
         </is>
       </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Sleep Support</t>
         </is>
       </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Fatty Liver</t>
         </is>
       </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Digestive Liver</t>
         </is>
       </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Lung Wellness</t>
         </is>
       </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Acidity</t>
         </is>
       </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Gas &amp; Bloating</t>
         </is>
       </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Constipation</t>
         </is>
       </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Appetite Support</t>
         </is>
       </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Weight Gain</t>
         </is>
       </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Metabolism Support</t>
         </is>
       </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Recurrent Respiratory Infections</t>
         </is>
       </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Chronic Constipation</t>
         </is>
       </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Menopause Symptoms</t>
         </is>
       </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Menstrual Disorders</t>
         </is>
       </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Hypothyroidism</t>
         </is>
       </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>PCOS</t>
         </is>
       </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>PCOD</t>
         </is>
       </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Thyroid</t>
         </is>
       </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>